--- a/output/yearly_population_iteration_61_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_61_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5411</v>
+        <v>5056</v>
       </c>
       <c r="C2" t="n">
-        <v>7027</v>
+        <v>8000</v>
       </c>
       <c r="D2" t="n">
-        <v>28894</v>
+        <v>37382</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3398</v>
+        <v>3148</v>
       </c>
       <c r="C3" t="n">
-        <v>6249</v>
+        <v>3989</v>
       </c>
       <c r="D3" t="n">
-        <v>13590</v>
+        <v>14784</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2500</v>
+        <v>2612</v>
       </c>
       <c r="C4" t="n">
-        <v>4309</v>
+        <v>5069</v>
       </c>
       <c r="D4" t="n">
-        <v>6913</v>
+        <v>8646</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1780</v>
+        <v>1616</v>
       </c>
       <c r="C5" t="n">
-        <v>4917</v>
+        <v>4626</v>
       </c>
       <c r="D5" t="n">
-        <v>2767</v>
+        <v>3559</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1094</v>
+        <v>914</v>
       </c>
       <c r="C6" t="n">
-        <v>3830</v>
+        <v>3066</v>
       </c>
       <c r="D6" t="n">
-        <v>1227</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>555</v>
+        <v>419</v>
       </c>
       <c r="C7" t="n">
-        <v>2173</v>
+        <v>1886</v>
       </c>
       <c r="D7" t="n">
-        <v>671</v>
+        <v>684</v>
       </c>
     </row>
     <row r="8">
@@ -864,10 +864,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>217</v>
+        <v>158</v>
       </c>
       <c r="C8" t="n">
-        <v>999</v>
+        <v>946</v>
       </c>
       <c r="D8" t="n">
         <v>432</v>
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="D9" t="n">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
         <v>219</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -940,7 +940,7 @@
         <v>97</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -951,7 +951,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D14" t="n">
         <v>100</v>
@@ -979,7 +979,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D16" t="n">
         <v>64</v>
@@ -993,7 +993,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1007,7 +1007,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1021,7 +1021,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>27</v>
@@ -1049,7 +1049,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D21" t="n">
         <v>8</v>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5983</v>
+        <v>5542</v>
       </c>
       <c r="C2" t="n">
-        <v>6754</v>
+        <v>11353</v>
       </c>
       <c r="D2" t="n">
-        <v>30544</v>
+        <v>35691</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3511</v>
+        <v>3240</v>
       </c>
       <c r="C3" t="n">
-        <v>5814</v>
+        <v>5089</v>
       </c>
       <c r="D3" t="n">
-        <v>14758</v>
+        <v>16863</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2457</v>
+        <v>2434</v>
       </c>
       <c r="C4" t="n">
-        <v>5131</v>
+        <v>4406</v>
       </c>
       <c r="D4" t="n">
-        <v>7792</v>
+        <v>9384</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1850</v>
+        <v>1815</v>
       </c>
       <c r="C5" t="n">
-        <v>4493</v>
+        <v>4733</v>
       </c>
       <c r="D5" t="n">
-        <v>3293</v>
+        <v>4198</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1261</v>
+        <v>1099</v>
       </c>
       <c r="C6" t="n">
-        <v>4273</v>
+        <v>3695</v>
       </c>
       <c r="D6" t="n">
-        <v>1447</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>707</v>
+        <v>560</v>
       </c>
       <c r="C7" t="n">
-        <v>2865</v>
+        <v>2405</v>
       </c>
       <c r="D7" t="n">
-        <v>739</v>
+        <v>765</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>311</v>
+        <v>235</v>
       </c>
       <c r="C8" t="n">
-        <v>1493</v>
+        <v>1332</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="C9" t="n">
-        <v>638</v>
+        <v>629</v>
       </c>
       <c r="D9" t="n">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C10" t="n">
         <v>291</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13">
@@ -1248,7 +1248,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D13" t="n">
         <v>125</v>
@@ -1262,10 +1262,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -1290,7 +1290,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D16" t="n">
         <v>64</v>
@@ -1304,7 +1304,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1318,7 +1318,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1332,7 +1332,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>27</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1360,7 +1360,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D21" t="n">
         <v>9</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8860</v>
+        <v>7022</v>
       </c>
       <c r="C2" t="n">
-        <v>10307</v>
+        <v>13443</v>
       </c>
       <c r="D2" t="n">
-        <v>28426</v>
+        <v>45775</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3655</v>
+        <v>3379</v>
       </c>
       <c r="C3" t="n">
-        <v>5503</v>
+        <v>6774</v>
       </c>
       <c r="D3" t="n">
-        <v>15707</v>
+        <v>18043</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2446</v>
+        <v>2348</v>
       </c>
       <c r="C4" t="n">
-        <v>5263</v>
+        <v>4609</v>
       </c>
       <c r="D4" t="n">
-        <v>8483</v>
+        <v>10085</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1864</v>
+        <v>1836</v>
       </c>
       <c r="C5" t="n">
-        <v>4619</v>
+        <v>4454</v>
       </c>
       <c r="D5" t="n">
-        <v>3840</v>
+        <v>4817</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1378</v>
+        <v>1257</v>
       </c>
       <c r="C6" t="n">
-        <v>4324</v>
+        <v>4044</v>
       </c>
       <c r="D6" t="n">
-        <v>1662</v>
+        <v>1958</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>828</v>
+        <v>691</v>
       </c>
       <c r="C7" t="n">
-        <v>3387</v>
+        <v>2922</v>
       </c>
       <c r="D7" t="n">
-        <v>828</v>
+        <v>879</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>407</v>
+        <v>320</v>
       </c>
       <c r="C8" t="n">
-        <v>2002</v>
+        <v>1728</v>
       </c>
       <c r="D8" t="n">
-        <v>488</v>
+        <v>493</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>162</v>
+        <v>124</v>
       </c>
       <c r="C9" t="n">
-        <v>956</v>
+        <v>884</v>
       </c>
       <c r="D9" t="n">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="C10" t="n">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12">
@@ -1548,7 +1548,7 @@
         <v>151</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15">
@@ -1604,7 +1604,7 @@
         <v>52</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1629,7 +1629,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1643,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>27</v>
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1671,7 +1671,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D21" t="n">
         <v>10</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7906</v>
+        <v>6373</v>
       </c>
       <c r="C2" t="n">
-        <v>7091</v>
+        <v>9248</v>
       </c>
       <c r="D2" t="n">
-        <v>23494</v>
+        <v>37486</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4388</v>
+        <v>4130</v>
       </c>
       <c r="C3" t="n">
-        <v>8660</v>
+        <v>9911</v>
       </c>
       <c r="D3" t="n">
-        <v>16930</v>
+        <v>19553</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1722</v>
+        <v>1696</v>
       </c>
       <c r="C4" t="n">
-        <v>7263</v>
+        <v>6797</v>
       </c>
       <c r="D4" t="n">
-        <v>8191</v>
+        <v>9912</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1273</v>
+        <v>1161</v>
       </c>
       <c r="C5" t="n">
-        <v>4237</v>
+        <v>3963</v>
       </c>
       <c r="D5" t="n">
-        <v>2660</v>
+        <v>3213</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>765</v>
+        <v>638</v>
       </c>
       <c r="C6" t="n">
-        <v>3319</v>
+        <v>2863</v>
       </c>
       <c r="D6" t="n">
-        <v>811</v>
+        <v>861</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>376</v>
+        <v>295</v>
       </c>
       <c r="C7" t="n">
-        <v>1961</v>
+        <v>1693</v>
       </c>
       <c r="D7" t="n">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>149</v>
+        <v>114</v>
       </c>
       <c r="C8" t="n">
-        <v>936</v>
+        <v>866</v>
       </c>
       <c r="D8" t="n">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="C9" t="n">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="D9" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D10" t="n">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="11">
@@ -1845,7 +1845,7 @@
         <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -1901,7 +1901,7 @@
         <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16">
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
         <v>38</v>
@@ -1940,7 +1940,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D18" t="n">
         <v>26</v>
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -1968,7 +1968,7 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D20" t="n">
         <v>10</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4620</v>
+        <v>3814</v>
       </c>
       <c r="C2" t="n">
-        <v>4097</v>
+        <v>3910</v>
       </c>
       <c r="D2" t="n">
-        <v>16368</v>
+        <v>26051</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4997</v>
+        <v>4361</v>
       </c>
       <c r="C3" t="n">
-        <v>7216</v>
+        <v>8720</v>
       </c>
       <c r="D3" t="n">
-        <v>17010</v>
+        <v>21053</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2386</v>
+        <v>2294</v>
       </c>
       <c r="C4" t="n">
-        <v>8034</v>
+        <v>8351</v>
       </c>
       <c r="D4" t="n">
-        <v>9279</v>
+        <v>11094</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1375</v>
+        <v>1280</v>
       </c>
       <c r="C5" t="n">
-        <v>5572</v>
+        <v>5213</v>
       </c>
       <c r="D5" t="n">
-        <v>3320</v>
+        <v>4013</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>901</v>
+        <v>761</v>
       </c>
       <c r="C6" t="n">
-        <v>3798</v>
+        <v>3379</v>
       </c>
       <c r="D6" t="n">
-        <v>1002</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="7">
@@ -2094,10 +2094,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>352</v>
+        <v>275</v>
       </c>
       <c r="C7" t="n">
-        <v>2492</v>
+        <v>2151</v>
       </c>
       <c r="D7" t="n">
         <v>528</v>
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="C8" t="n">
-        <v>1228</v>
+        <v>1120</v>
       </c>
       <c r="D8" t="n">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C9" t="n">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D9" t="n">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="10">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D12" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13">
@@ -2198,7 +2198,7 @@
         <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15">
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D16" t="n">
         <v>37</v>
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D17" t="n">
         <v>25</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2265,7 +2265,7 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D19" t="n">
         <v>9</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4416</v>
+        <v>3310</v>
       </c>
       <c r="C2" t="n">
-        <v>4977</v>
+        <v>5698</v>
       </c>
       <c r="D2" t="n">
-        <v>24846</v>
+        <v>29691</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4064</v>
+        <v>3473</v>
       </c>
       <c r="C3" t="n">
-        <v>5065</v>
+        <v>5780</v>
       </c>
       <c r="D3" t="n">
-        <v>15779</v>
+        <v>20317</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3005</v>
+        <v>2735</v>
       </c>
       <c r="C4" t="n">
-        <v>7543</v>
+        <v>8354</v>
       </c>
       <c r="D4" t="n">
-        <v>10258</v>
+        <v>12382</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1598</v>
+        <v>1511</v>
       </c>
       <c r="C5" t="n">
-        <v>6590</v>
+        <v>6550</v>
       </c>
       <c r="D5" t="n">
-        <v>4134</v>
+        <v>4978</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1010</v>
+        <v>892</v>
       </c>
       <c r="C6" t="n">
-        <v>4582</v>
+        <v>4189</v>
       </c>
       <c r="D6" t="n">
-        <v>1322</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>500</v>
+        <v>407</v>
       </c>
       <c r="C7" t="n">
-        <v>3041</v>
+        <v>2667</v>
       </c>
       <c r="D7" t="n">
-        <v>587</v>
+        <v>602</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>177</v>
+        <v>139</v>
       </c>
       <c r="C8" t="n">
-        <v>1747</v>
+        <v>1544</v>
       </c>
       <c r="D8" t="n">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>747</v>
+        <v>708</v>
       </c>
       <c r="D9" t="n">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="10">
@@ -2450,7 +2450,7 @@
         <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D10" t="n">
         <v>211</v>
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="D11" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12">
@@ -2481,7 +2481,7 @@
         <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2509,7 +2509,7 @@
         <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
         <v>49</v>
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D16" t="n">
         <v>36</v>
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D17" t="n">
         <v>23</v>
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2653</v>
+        <v>1989</v>
       </c>
       <c r="C2" t="n">
-        <v>2396</v>
+        <v>2724</v>
       </c>
       <c r="D2" t="n">
-        <v>17320</v>
+        <v>20678</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4001</v>
+        <v>3315</v>
       </c>
       <c r="C3" t="n">
-        <v>4841</v>
+        <v>5586</v>
       </c>
       <c r="D3" t="n">
-        <v>16368</v>
+        <v>20836</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3320</v>
+        <v>3008</v>
       </c>
       <c r="C4" t="n">
-        <v>7373</v>
+        <v>8166</v>
       </c>
       <c r="D4" t="n">
-        <v>10955</v>
+        <v>13333</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1698</v>
+        <v>1572</v>
       </c>
       <c r="C5" t="n">
-        <v>7800</v>
+        <v>7904</v>
       </c>
       <c r="D5" t="n">
-        <v>4366</v>
+        <v>5250</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>863</v>
+        <v>730</v>
       </c>
       <c r="C6" t="n">
-        <v>5520</v>
+        <v>5035</v>
       </c>
       <c r="D6" t="n">
-        <v>1296</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>163</v>
+        <v>128</v>
       </c>
       <c r="C7" t="n">
-        <v>3178</v>
+        <v>2810</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>595</v>
       </c>
     </row>
     <row r="8">
@@ -2730,10 +2730,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="C8" t="n">
-        <v>1262</v>
+        <v>1147</v>
       </c>
       <c r="D8" t="n">
         <v>375</v>
@@ -2747,10 +2747,10 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D10" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11">
@@ -2778,7 +2778,7 @@
         <v>110</v>
       </c>
       <c r="D11" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12">
@@ -2806,7 +2806,7 @@
         <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
         <v>48</v>
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D15" t="n">
         <v>35</v>
@@ -2845,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D16" t="n">
         <v>22</v>
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2750</v>
+        <v>3281</v>
       </c>
       <c r="C2" t="n">
-        <v>6017</v>
+        <v>5394</v>
       </c>
       <c r="D2" t="n">
-        <v>15836</v>
+        <v>18107</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2949</v>
+        <v>2387</v>
       </c>
       <c r="C3" t="n">
-        <v>3328</v>
+        <v>3856</v>
       </c>
       <c r="D3" t="n">
-        <v>15554</v>
+        <v>19614</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3168</v>
+        <v>2739</v>
       </c>
       <c r="C4" t="n">
-        <v>6099</v>
+        <v>6807</v>
       </c>
       <c r="D4" t="n">
-        <v>11453</v>
+        <v>14080</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2072</v>
+        <v>1899</v>
       </c>
       <c r="C5" t="n">
-        <v>7524</v>
+        <v>7931</v>
       </c>
       <c r="D5" t="n">
-        <v>5182</v>
+        <v>6254</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1068</v>
+        <v>949</v>
       </c>
       <c r="C6" t="n">
-        <v>6465</v>
+        <v>6223</v>
       </c>
       <c r="D6" t="n">
-        <v>1691</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>334</v>
+        <v>268</v>
       </c>
       <c r="C7" t="n">
-        <v>4125</v>
+        <v>3736</v>
       </c>
       <c r="D7" t="n">
-        <v>674</v>
+        <v>705</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="C8" t="n">
-        <v>1993</v>
+        <v>1755</v>
       </c>
       <c r="D8" t="n">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="9">
@@ -3055,10 +3055,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>604</v>
+        <v>572</v>
       </c>
       <c r="D9" t="n">
         <v>291</v>
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D10" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -3100,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D12" t="n">
         <v>100</v>
@@ -3117,7 +3117,7 @@
         <v>59</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D15" t="n">
         <v>33</v>
@@ -3156,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D16" t="n">
         <v>20</v>
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D17" t="n">
         <v>9</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1999</v>
+        <v>2086</v>
       </c>
       <c r="C2" t="n">
-        <v>4609</v>
+        <v>3919</v>
       </c>
       <c r="D2" t="n">
-        <v>11881</v>
+        <v>13098</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2528</v>
+        <v>2336</v>
       </c>
       <c r="C3" t="n">
-        <v>3971</v>
+        <v>4082</v>
       </c>
       <c r="D3" t="n">
-        <v>14741</v>
+        <v>18554</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2859</v>
+        <v>2410</v>
       </c>
       <c r="C4" t="n">
-        <v>5030</v>
+        <v>5634</v>
       </c>
       <c r="D4" t="n">
-        <v>11875</v>
+        <v>14477</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2259</v>
+        <v>2057</v>
       </c>
       <c r="C5" t="n">
-        <v>7078</v>
+        <v>7671</v>
       </c>
       <c r="D5" t="n">
-        <v>5736</v>
+        <v>6950</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1260</v>
+        <v>1109</v>
       </c>
       <c r="C6" t="n">
-        <v>7126</v>
+        <v>6995</v>
       </c>
       <c r="D6" t="n">
-        <v>2022</v>
+        <v>2361</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>302</v>
+        <v>240</v>
       </c>
       <c r="C7" t="n">
-        <v>4916</v>
+        <v>4575</v>
       </c>
       <c r="D7" t="n">
-        <v>748</v>
+        <v>791</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>2551</v>
+        <v>2228</v>
       </c>
       <c r="D8" t="n">
-        <v>409</v>
+        <v>413</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>687</v>
+        <v>651</v>
       </c>
       <c r="D9" t="n">
-        <v>290</v>
+        <v>287</v>
       </c>
     </row>
     <row r="10">
@@ -3386,7 +3386,7 @@
         <v>223</v>
       </c>
       <c r="D10" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3414,7 +3414,7 @@
         <v>78</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D13" t="n">
         <v>63</v>
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D14" t="n">
         <v>36</v>
@@ -3453,7 +3453,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
         <v>19</v>
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4672</v>
+        <v>3903</v>
       </c>
       <c r="C2" t="n">
-        <v>9484</v>
+        <v>10725</v>
       </c>
       <c r="D2" t="n">
-        <v>23430</v>
+        <v>16539</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1970</v>
+        <v>1894</v>
       </c>
       <c r="C3" t="n">
-        <v>3757</v>
+        <v>3613</v>
       </c>
       <c r="D3" t="n">
-        <v>13454</v>
+        <v>16711</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2407</v>
+        <v>2072</v>
       </c>
       <c r="C4" t="n">
-        <v>4478</v>
+        <v>4876</v>
       </c>
       <c r="D4" t="n">
-        <v>11926</v>
+        <v>14623</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2244</v>
+        <v>2008</v>
       </c>
       <c r="C5" t="n">
-        <v>6105</v>
+        <v>6709</v>
       </c>
       <c r="D5" t="n">
-        <v>6386</v>
+        <v>7750</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1485</v>
+        <v>1318</v>
       </c>
       <c r="C6" t="n">
-        <v>7047</v>
+        <v>7190</v>
       </c>
       <c r="D6" t="n">
-        <v>2459</v>
+        <v>2903</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>535</v>
+        <v>445</v>
       </c>
       <c r="C7" t="n">
-        <v>5737</v>
+        <v>5450</v>
       </c>
       <c r="D7" t="n">
-        <v>890</v>
+        <v>967</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="C8" t="n">
-        <v>3409</v>
+        <v>3053</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>449</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>1296</v>
+        <v>1145</v>
       </c>
       <c r="D9" t="n">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10">
@@ -3694,7 +3694,7 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="D10" t="n">
         <v>184</v>
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8430</v>
+        <v>4540</v>
       </c>
       <c r="C2" t="n">
-        <v>9412</v>
+        <v>9307</v>
       </c>
       <c r="D2" t="n">
-        <v>19938</v>
+        <v>11587</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3375</v>
+        <v>2818</v>
       </c>
       <c r="C2" t="n">
-        <v>5462</v>
+        <v>6263</v>
       </c>
       <c r="D2" t="n">
-        <v>17431</v>
+        <v>12305</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2831</v>
+        <v>2596</v>
       </c>
       <c r="C3" t="n">
-        <v>5370</v>
+        <v>5438</v>
       </c>
       <c r="D3" t="n">
-        <v>15029</v>
+        <v>17951</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3303</v>
+        <v>2912</v>
       </c>
       <c r="C4" t="n">
-        <v>6593</v>
+        <v>7153</v>
       </c>
       <c r="D4" t="n">
-        <v>12180</v>
+        <v>14915</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1413</v>
+        <v>1254</v>
       </c>
       <c r="C5" t="n">
-        <v>9520</v>
+        <v>10022</v>
       </c>
       <c r="D5" t="n">
-        <v>5802</v>
+        <v>7002</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>494</v>
+        <v>411</v>
       </c>
       <c r="C6" t="n">
-        <v>6934</v>
+        <v>6679</v>
       </c>
       <c r="D6" t="n">
-        <v>1963</v>
+        <v>2246</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="C7" t="n">
-        <v>3340</v>
+        <v>2991</v>
       </c>
       <c r="D7" t="n">
-        <v>545</v>
+        <v>563</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C8" t="n">
-        <v>1270</v>
+        <v>1122</v>
       </c>
       <c r="D8" t="n">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="9">
@@ -4302,7 +4302,7 @@
         <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="D9" t="n">
         <v>180</v>
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D10" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D11" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D13" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7446</v>
+        <v>6319</v>
       </c>
       <c r="C2" t="n">
-        <v>5737</v>
+        <v>5844</v>
       </c>
       <c r="D2" t="n">
-        <v>18345</v>
+        <v>31204</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3580</v>
+        <v>1930</v>
       </c>
       <c r="C3" t="n">
-        <v>4743</v>
+        <v>4690</v>
       </c>
       <c r="D3" t="n">
-        <v>3988</v>
+        <v>2585</v>
       </c>
     </row>
     <row r="4">
@@ -4557,7 +4557,7 @@
         <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4571,7 +4571,7 @@
         <v>200</v>
       </c>
       <c r="C6" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D6" t="n">
         <v>816</v>
@@ -4585,7 +4585,7 @@
         <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="D7" t="n">
         <v>538</v>
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C8" t="n">
         <v>260</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C9" t="n">
         <v>205</v>
       </c>
       <c r="D9" t="n">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>180</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="11">
@@ -4638,7 +4638,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
         <v>154</v>
@@ -4697,7 +4697,7 @@
         <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D15" t="n">
         <v>118</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4689</v>
+        <v>4754</v>
       </c>
       <c r="C2" t="n">
-        <v>8845</v>
+        <v>4712</v>
       </c>
       <c r="D2" t="n">
-        <v>16689</v>
+        <v>24364</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4532</v>
+        <v>3383</v>
       </c>
       <c r="C3" t="n">
-        <v>4575</v>
+        <v>4607</v>
       </c>
       <c r="D3" t="n">
-        <v>6106</v>
+        <v>7202</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1589</v>
+        <v>872</v>
       </c>
       <c r="C4" t="n">
-        <v>2823</v>
+        <v>2792</v>
       </c>
       <c r="D4" t="n">
-        <v>1985</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="5">
@@ -4868,7 +4868,7 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D5" t="n">
         <v>1198</v>
@@ -4882,7 +4882,7 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="D6" t="n">
         <v>859</v>
@@ -4896,7 +4896,7 @@
         <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="D7" t="n">
         <v>584</v>
@@ -4910,10 +4910,10 @@
         <v>114</v>
       </c>
       <c r="C8" t="n">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>443</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -4927,7 +4927,7 @@
         <v>232</v>
       </c>
       <c r="D9" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="10">
@@ -4941,7 +4941,7 @@
         <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="11">
@@ -5022,7 +5022,7 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4948</v>
+        <v>4831</v>
       </c>
       <c r="C2" t="n">
-        <v>10453</v>
+        <v>7110</v>
       </c>
       <c r="D2" t="n">
-        <v>14387</v>
+        <v>38762</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3845</v>
+        <v>3333</v>
       </c>
       <c r="C3" t="n">
-        <v>5948</v>
+        <v>4043</v>
       </c>
       <c r="D3" t="n">
-        <v>7359</v>
+        <v>9429</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2570</v>
+        <v>1806</v>
       </c>
       <c r="C4" t="n">
-        <v>3739</v>
+        <v>3717</v>
       </c>
       <c r="D4" t="n">
-        <v>2715</v>
+        <v>2706</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>699</v>
+        <v>411</v>
       </c>
       <c r="C5" t="n">
-        <v>1614</v>
+        <v>1624</v>
       </c>
       <c r="D5" t="n">
-        <v>1293</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="6">
@@ -5190,10 +5190,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D6" t="n">
         <v>908</v>
@@ -5204,7 +5204,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
         <v>407</v>
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D8" t="n">
-        <v>457</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C9" t="n">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10">
@@ -5252,7 +5252,7 @@
         <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C11" t="n">
         <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="12">
@@ -5333,7 +5333,7 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
         <v>100</v>
@@ -5347,7 +5347,7 @@
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
         <v>78</v>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5424</v>
+        <v>4688</v>
       </c>
       <c r="C2" t="n">
-        <v>8440</v>
+        <v>9092</v>
       </c>
       <c r="D2" t="n">
-        <v>24852</v>
+        <v>29105</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3589</v>
+        <v>3311</v>
       </c>
       <c r="C3" t="n">
-        <v>7168</v>
+        <v>4874</v>
       </c>
       <c r="D3" t="n">
-        <v>7909</v>
+        <v>13223</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2711</v>
+        <v>2152</v>
       </c>
       <c r="C4" t="n">
-        <v>4791</v>
+        <v>3776</v>
       </c>
       <c r="D4" t="n">
-        <v>3479</v>
+        <v>3850</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1353</v>
+        <v>908</v>
       </c>
       <c r="C5" t="n">
-        <v>2682</v>
+        <v>2675</v>
       </c>
       <c r="D5" t="n">
-        <v>1487</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>356</v>
+        <v>242</v>
       </c>
       <c r="C6" t="n">
-        <v>956</v>
+        <v>960</v>
       </c>
       <c r="D6" t="n">
-        <v>961</v>
+        <v>953</v>
       </c>
     </row>
     <row r="7">
@@ -5518,7 +5518,7 @@
         <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D7" t="n">
         <v>666</v>
@@ -5532,10 +5532,10 @@
         <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D8" t="n">
-        <v>474</v>
+        <v>471</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D9" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C10" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D10" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11">
@@ -5577,7 +5577,7 @@
         <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="12">
@@ -5585,7 +5585,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12" t="n">
         <v>158</v>
@@ -5644,7 +5644,7 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
         <v>101</v>
@@ -5658,7 +5658,7 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
         <v>78</v>
@@ -5672,7 +5672,7 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
         <v>60</v>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5602</v>
+        <v>6122</v>
       </c>
       <c r="C2" t="n">
-        <v>5470</v>
+        <v>8710</v>
       </c>
       <c r="D2" t="n">
-        <v>26958</v>
+        <v>24452</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3240</v>
+        <v>2919</v>
       </c>
       <c r="C3" t="n">
-        <v>6399</v>
+        <v>5728</v>
       </c>
       <c r="D3" t="n">
-        <v>9339</v>
+        <v>13836</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1934</v>
+        <v>1673</v>
       </c>
       <c r="C4" t="n">
-        <v>4972</v>
+        <v>3547</v>
       </c>
       <c r="D4" t="n">
-        <v>3644</v>
+        <v>4751</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1058</v>
+        <v>787</v>
       </c>
       <c r="C5" t="n">
-        <v>2722</v>
+        <v>2367</v>
       </c>
       <c r="D5" t="n">
-        <v>1435</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>402</v>
+        <v>271</v>
       </c>
       <c r="C6" t="n">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="D6" t="n">
-        <v>799</v>
+        <v>789</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>106</v>
+        <v>85</v>
       </c>
       <c r="C7" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>523</v>
+        <v>518</v>
       </c>
     </row>
     <row r="8">
@@ -5846,7 +5846,7 @@
         <v>223</v>
       </c>
       <c r="D8" t="n">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="9">
@@ -5857,7 +5857,7 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D9" t="n">
         <v>272</v>
@@ -5871,10 +5871,10 @@
         <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D10" t="n">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11">
@@ -5885,7 +5885,7 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
         <v>195</v>
@@ -5899,10 +5899,10 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13">
@@ -5910,10 +5910,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D13" t="n">
         <v>117</v>
@@ -5927,7 +5927,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
         <v>96</v>
@@ -5955,7 +5955,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D16" t="n">
         <v>64</v>
@@ -5969,7 +5969,7 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
         <v>50</v>
@@ -5983,7 +5983,7 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -5997,7 +5997,7 @@
         <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>26</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4673</v>
+        <v>5402</v>
       </c>
       <c r="C2" t="n">
-        <v>3672</v>
+        <v>4837</v>
       </c>
       <c r="D2" t="n">
-        <v>25189</v>
+        <v>20328</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3655</v>
+        <v>3740</v>
       </c>
       <c r="C3" t="n">
-        <v>5047</v>
+        <v>6409</v>
       </c>
       <c r="D3" t="n">
-        <v>11611</v>
+        <v>14601</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2259</v>
+        <v>2005</v>
       </c>
       <c r="C4" t="n">
-        <v>5717</v>
+        <v>4737</v>
       </c>
       <c r="D4" t="n">
-        <v>4681</v>
+        <v>6438</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1322</v>
+        <v>1083</v>
       </c>
       <c r="C5" t="n">
-        <v>3935</v>
+        <v>3008</v>
       </c>
       <c r="D5" t="n">
-        <v>1801</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>675</v>
+        <v>489</v>
       </c>
       <c r="C6" t="n">
-        <v>2055</v>
+        <v>1853</v>
       </c>
       <c r="D6" t="n">
-        <v>909</v>
+        <v>906</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>228</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
         <v>860</v>
       </c>
       <c r="D7" t="n">
-        <v>563</v>
+        <v>558</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C8" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D8" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="9">
@@ -6171,7 +6171,7 @@
         <v>209</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D10" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11">
@@ -6196,7 +6196,7 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
         <v>199</v>
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14">
@@ -6235,7 +6235,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
         <v>63</v>
@@ -6280,7 +6280,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -6294,7 +6294,7 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -6308,7 +6308,7 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>26</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5030</v>
+        <v>3890</v>
       </c>
       <c r="C2" t="n">
-        <v>10761</v>
+        <v>4300</v>
       </c>
       <c r="D2" t="n">
-        <v>23599</v>
+        <v>23589</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3413</v>
+        <v>3731</v>
       </c>
       <c r="C3" t="n">
-        <v>3738</v>
+        <v>4828</v>
       </c>
       <c r="D3" t="n">
-        <v>12947</v>
+        <v>14466</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2514</v>
+        <v>2434</v>
       </c>
       <c r="C4" t="n">
-        <v>5225</v>
+        <v>5569</v>
       </c>
       <c r="D4" t="n">
-        <v>5869</v>
+        <v>7809</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1576</v>
+        <v>1353</v>
       </c>
       <c r="C5" t="n">
-        <v>4811</v>
+        <v>3846</v>
       </c>
       <c r="D5" t="n">
-        <v>2271</v>
+        <v>2774</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>898</v>
+        <v>703</v>
       </c>
       <c r="C6" t="n">
-        <v>2986</v>
+        <v>2441</v>
       </c>
       <c r="D6" t="n">
-        <v>1041</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>396</v>
+        <v>284</v>
       </c>
       <c r="C7" t="n">
-        <v>1480</v>
+        <v>1375</v>
       </c>
       <c r="D7" t="n">
-        <v>618</v>
+        <v>613</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>128</v>
+        <v>98</v>
       </c>
       <c r="C8" t="n">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D8" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="D10" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
         <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14">
@@ -6546,10 +6546,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
         <v>99</v>
@@ -6577,7 +6577,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D16" t="n">
         <v>64</v>
@@ -6591,7 +6591,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -6605,7 +6605,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -6619,7 +6619,7 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>27</v>
@@ -6647,7 +6647,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D21" t="n">
         <v>7</v>

--- a/output/yearly_population_iteration_61_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_61_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5056</v>
+        <v>6387</v>
       </c>
       <c r="C2" t="n">
-        <v>8000</v>
+        <v>6275</v>
       </c>
       <c r="D2" t="n">
-        <v>37382</v>
+        <v>33789</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3148</v>
+        <v>4208</v>
       </c>
       <c r="C3" t="n">
-        <v>3989</v>
+        <v>5401</v>
       </c>
       <c r="D3" t="n">
-        <v>14784</v>
+        <v>14567</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2612</v>
+        <v>2770</v>
       </c>
       <c r="C4" t="n">
-        <v>5069</v>
+        <v>3628</v>
       </c>
       <c r="D4" t="n">
-        <v>8646</v>
+        <v>7482</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1616</v>
+        <v>1812</v>
       </c>
       <c r="C5" t="n">
-        <v>4626</v>
+        <v>3084</v>
       </c>
       <c r="D5" t="n">
-        <v>3559</v>
+        <v>2733</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>914</v>
+        <v>1050</v>
       </c>
       <c r="C6" t="n">
-        <v>3066</v>
+        <v>2725</v>
       </c>
       <c r="D6" t="n">
-        <v>1330</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>419</v>
+        <v>479</v>
       </c>
       <c r="C7" t="n">
-        <v>1886</v>
+        <v>1925</v>
       </c>
       <c r="D7" t="n">
-        <v>684</v>
+        <v>650</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="C8" t="n">
-        <v>946</v>
+        <v>996</v>
       </c>
       <c r="D8" t="n">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C9" t="n">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="D9" t="n">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
         <v>219</v>
       </c>
       <c r="D10" t="n">
-        <v>245</v>
+        <v>242</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="D11" t="n">
-        <v>201</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1049,7 +1049,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D21" t="n">
         <v>8</v>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5542</v>
+        <v>7282</v>
       </c>
       <c r="C2" t="n">
-        <v>11353</v>
+        <v>6718</v>
       </c>
       <c r="D2" t="n">
-        <v>35691</v>
+        <v>31318</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3240</v>
+        <v>4225</v>
       </c>
       <c r="C3" t="n">
-        <v>5089</v>
+        <v>5100</v>
       </c>
       <c r="D3" t="n">
-        <v>16863</v>
+        <v>16202</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2434</v>
+        <v>2898</v>
       </c>
       <c r="C4" t="n">
-        <v>4406</v>
+        <v>4420</v>
       </c>
       <c r="D4" t="n">
-        <v>9384</v>
+        <v>8338</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1815</v>
+        <v>1988</v>
       </c>
       <c r="C5" t="n">
-        <v>4733</v>
+        <v>3246</v>
       </c>
       <c r="D5" t="n">
-        <v>4198</v>
+        <v>3424</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1099</v>
+        <v>1254</v>
       </c>
       <c r="C6" t="n">
-        <v>3695</v>
+        <v>2863</v>
       </c>
       <c r="D6" t="n">
-        <v>1654</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>560</v>
+        <v>647</v>
       </c>
       <c r="C7" t="n">
-        <v>2405</v>
+        <v>2284</v>
       </c>
       <c r="D7" t="n">
-        <v>765</v>
+        <v>724</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>235</v>
+        <v>264</v>
       </c>
       <c r="C8" t="n">
-        <v>1332</v>
+        <v>1386</v>
       </c>
       <c r="D8" t="n">
-        <v>464</v>
+        <v>453</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C9" t="n">
-        <v>629</v>
+        <v>660</v>
       </c>
       <c r="D9" t="n">
-        <v>317</v>
+        <v>324</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C10" t="n">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1360,7 +1360,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D21" t="n">
         <v>9</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7022</v>
+        <v>8503</v>
       </c>
       <c r="C2" t="n">
-        <v>13443</v>
+        <v>7541</v>
       </c>
       <c r="D2" t="n">
-        <v>45775</v>
+        <v>33206</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3379</v>
+        <v>4467</v>
       </c>
       <c r="C3" t="n">
-        <v>6774</v>
+        <v>5116</v>
       </c>
       <c r="D3" t="n">
-        <v>18043</v>
+        <v>17073</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2348</v>
+        <v>2959</v>
       </c>
       <c r="C4" t="n">
-        <v>4609</v>
+        <v>4585</v>
       </c>
       <c r="D4" t="n">
-        <v>10085</v>
+        <v>9292</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1836</v>
+        <v>2089</v>
       </c>
       <c r="C5" t="n">
-        <v>4454</v>
+        <v>3654</v>
       </c>
       <c r="D5" t="n">
-        <v>4817</v>
+        <v>3994</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1257</v>
+        <v>1414</v>
       </c>
       <c r="C6" t="n">
-        <v>4044</v>
+        <v>2998</v>
       </c>
       <c r="D6" t="n">
-        <v>1958</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>691</v>
+        <v>800</v>
       </c>
       <c r="C7" t="n">
-        <v>2922</v>
+        <v>2499</v>
       </c>
       <c r="D7" t="n">
-        <v>879</v>
+        <v>799</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>320</v>
+        <v>366</v>
       </c>
       <c r="C8" t="n">
-        <v>1728</v>
+        <v>1746</v>
       </c>
       <c r="D8" t="n">
-        <v>493</v>
+        <v>485</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="C9" t="n">
-        <v>884</v>
+        <v>930</v>
       </c>
       <c r="D9" t="n">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C10" t="n">
-        <v>413</v>
+        <v>427</v>
       </c>
       <c r="D10" t="n">
-        <v>252</v>
+        <v>255</v>
       </c>
     </row>
     <row r="11">
@@ -1528,10 +1528,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="D11" t="n">
         <v>205</v>
@@ -1545,7 +1545,7 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="D12" t="n">
         <v>165</v>
@@ -1559,10 +1559,10 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1601,7 +1601,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -1615,7 +1615,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1671,7 +1671,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D21" t="n">
         <v>10</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6373</v>
+        <v>7763</v>
       </c>
       <c r="C2" t="n">
-        <v>9248</v>
+        <v>5067</v>
       </c>
       <c r="D2" t="n">
-        <v>37486</v>
+        <v>27220</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4130</v>
+        <v>5375</v>
       </c>
       <c r="C3" t="n">
-        <v>9911</v>
+        <v>7681</v>
       </c>
       <c r="D3" t="n">
-        <v>19553</v>
+        <v>18499</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1696</v>
+        <v>1930</v>
       </c>
       <c r="C4" t="n">
-        <v>6797</v>
+        <v>6104</v>
       </c>
       <c r="D4" t="n">
-        <v>9912</v>
+        <v>8877</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1161</v>
+        <v>1306</v>
       </c>
       <c r="C5" t="n">
-        <v>3963</v>
+        <v>2938</v>
       </c>
       <c r="D5" t="n">
-        <v>3213</v>
+        <v>2735</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>638</v>
+        <v>739</v>
       </c>
       <c r="C6" t="n">
-        <v>2863</v>
+        <v>2449</v>
       </c>
       <c r="D6" t="n">
-        <v>861</v>
+        <v>783</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>295</v>
+        <v>338</v>
       </c>
       <c r="C7" t="n">
-        <v>1693</v>
+        <v>1711</v>
       </c>
       <c r="D7" t="n">
-        <v>483</v>
+        <v>475</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="C8" t="n">
-        <v>866</v>
+        <v>911</v>
       </c>
       <c r="D8" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C9" t="n">
-        <v>404</v>
+        <v>418</v>
       </c>
       <c r="D9" t="n">
-        <v>246</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10">
@@ -1825,10 +1825,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="D10" t="n">
         <v>200</v>
@@ -1842,7 +1842,7 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
         <v>161</v>
@@ -1856,10 +1856,10 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D12" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15">
@@ -1898,7 +1898,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D15" t="n">
         <v>63</v>
@@ -1912,7 +1912,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D16" t="n">
         <v>50</v>
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -1968,7 +1968,7 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
         <v>10</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3814</v>
+        <v>4645</v>
       </c>
       <c r="C2" t="n">
-        <v>3910</v>
+        <v>2402</v>
       </c>
       <c r="D2" t="n">
-        <v>26051</v>
+        <v>19607</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4361</v>
+        <v>5522</v>
       </c>
       <c r="C3" t="n">
-        <v>8720</v>
+        <v>5868</v>
       </c>
       <c r="D3" t="n">
-        <v>21053</v>
+        <v>18619</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2294</v>
+        <v>2819</v>
       </c>
       <c r="C4" t="n">
-        <v>8351</v>
+        <v>6894</v>
       </c>
       <c r="D4" t="n">
-        <v>11094</v>
+        <v>10255</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1280</v>
+        <v>1465</v>
       </c>
       <c r="C5" t="n">
-        <v>5213</v>
+        <v>4355</v>
       </c>
       <c r="D5" t="n">
-        <v>4013</v>
+        <v>3470</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>761</v>
+        <v>886</v>
       </c>
       <c r="C6" t="n">
-        <v>3379</v>
+        <v>2771</v>
       </c>
       <c r="D6" t="n">
-        <v>1110</v>
+        <v>983</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>275</v>
+        <v>316</v>
       </c>
       <c r="C7" t="n">
-        <v>2151</v>
+        <v>2046</v>
       </c>
       <c r="D7" t="n">
-        <v>528</v>
+        <v>519</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="C8" t="n">
-        <v>1120</v>
+        <v>1187</v>
       </c>
       <c r="D8" t="n">
-        <v>334</v>
+        <v>340</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C9" t="n">
-        <v>450</v>
+        <v>477</v>
       </c>
       <c r="D9" t="n">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="10">
@@ -2139,7 +2139,7 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="D10" t="n">
         <v>209</v>
@@ -2153,10 +2153,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D15" t="n">
         <v>49</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2265,7 +2265,7 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D19" t="n">
         <v>9</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3310</v>
+        <v>4732</v>
       </c>
       <c r="C2" t="n">
-        <v>5698</v>
+        <v>5838</v>
       </c>
       <c r="D2" t="n">
-        <v>29691</v>
+        <v>18642</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3473</v>
+        <v>4326</v>
       </c>
       <c r="C3" t="n">
-        <v>5780</v>
+        <v>3722</v>
       </c>
       <c r="D3" t="n">
-        <v>20317</v>
+        <v>17480</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2735</v>
+        <v>3417</v>
       </c>
       <c r="C4" t="n">
-        <v>8354</v>
+        <v>6238</v>
       </c>
       <c r="D4" t="n">
-        <v>12382</v>
+        <v>11388</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1511</v>
+        <v>1813</v>
       </c>
       <c r="C5" t="n">
-        <v>6550</v>
+        <v>5483</v>
       </c>
       <c r="D5" t="n">
-        <v>4978</v>
+        <v>4471</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>892</v>
+        <v>1049</v>
       </c>
       <c r="C6" t="n">
-        <v>4189</v>
+        <v>3500</v>
       </c>
       <c r="D6" t="n">
-        <v>1513</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>407</v>
+        <v>477</v>
       </c>
       <c r="C7" t="n">
-        <v>2667</v>
+        <v>2384</v>
       </c>
       <c r="D7" t="n">
-        <v>602</v>
+        <v>581</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>139</v>
+        <v>158</v>
       </c>
       <c r="C8" t="n">
-        <v>1544</v>
+        <v>1551</v>
       </c>
       <c r="D8" t="n">
-        <v>355</v>
+        <v>364</v>
       </c>
     </row>
     <row r="9">
@@ -2433,10 +2433,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C9" t="n">
-        <v>708</v>
+        <v>752</v>
       </c>
       <c r="D9" t="n">
         <v>264</v>
@@ -2450,10 +2450,10 @@
         <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>304</v>
+        <v>324</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D13" t="n">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2523,7 +2523,7 @@
         <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D16" t="n">
         <v>36</v>
@@ -2551,7 +2551,7 @@
         <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D19" t="n">
         <v>6</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1989</v>
+        <v>2782</v>
       </c>
       <c r="C2" t="n">
-        <v>2724</v>
+        <v>2692</v>
       </c>
       <c r="D2" t="n">
-        <v>20678</v>
+        <v>12870</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3315</v>
+        <v>4268</v>
       </c>
       <c r="C3" t="n">
-        <v>5586</v>
+        <v>4330</v>
       </c>
       <c r="D3" t="n">
-        <v>20836</v>
+        <v>17190</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3008</v>
+        <v>3782</v>
       </c>
       <c r="C4" t="n">
-        <v>8166</v>
+        <v>5861</v>
       </c>
       <c r="D4" t="n">
-        <v>13333</v>
+        <v>12173</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1572</v>
+        <v>1890</v>
       </c>
       <c r="C5" t="n">
-        <v>7904</v>
+        <v>6409</v>
       </c>
       <c r="D5" t="n">
-        <v>5250</v>
+        <v>4875</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>730</v>
+        <v>876</v>
       </c>
       <c r="C6" t="n">
-        <v>5035</v>
+        <v>4385</v>
       </c>
       <c r="D6" t="n">
-        <v>1467</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>2810</v>
+        <v>2645</v>
       </c>
       <c r="D7" t="n">
-        <v>595</v>
+        <v>586</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C8" t="n">
-        <v>1147</v>
+        <v>1223</v>
       </c>
       <c r="D8" t="n">
-        <v>375</v>
+        <v>381</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>297</v>
+        <v>317</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>289</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="D10" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13">
@@ -2820,7 +2820,7 @@
         <v>43</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D15" t="n">
         <v>35</v>
@@ -2848,7 +2848,7 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D18" t="n">
         <v>5</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3281</v>
+        <v>3718</v>
       </c>
       <c r="C2" t="n">
-        <v>5394</v>
+        <v>4139</v>
       </c>
       <c r="D2" t="n">
-        <v>18107</v>
+        <v>14765</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2387</v>
+        <v>3116</v>
       </c>
       <c r="C3" t="n">
-        <v>3856</v>
+        <v>3135</v>
       </c>
       <c r="D3" t="n">
-        <v>19614</v>
+        <v>15447</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2739</v>
+        <v>3484</v>
       </c>
       <c r="C4" t="n">
-        <v>6807</v>
+        <v>5045</v>
       </c>
       <c r="D4" t="n">
-        <v>14080</v>
+        <v>12621</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1899</v>
+        <v>2362</v>
       </c>
       <c r="C5" t="n">
-        <v>7931</v>
+        <v>6084</v>
       </c>
       <c r="D5" t="n">
-        <v>6254</v>
+        <v>5847</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>949</v>
+        <v>1159</v>
       </c>
       <c r="C6" t="n">
-        <v>6223</v>
+        <v>5261</v>
       </c>
       <c r="D6" t="n">
-        <v>1956</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>268</v>
+        <v>331</v>
       </c>
       <c r="C7" t="n">
-        <v>3736</v>
+        <v>3411</v>
       </c>
       <c r="D7" t="n">
-        <v>705</v>
+        <v>672</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>1755</v>
+        <v>1776</v>
       </c>
       <c r="D8" t="n">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>572</v>
+        <v>628</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="D10" t="n">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D12" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D13" t="n">
         <v>61</v>
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D14" t="n">
         <v>47</v>
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -3156,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D16" t="n">
         <v>20</v>
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2086</v>
+        <v>2715</v>
       </c>
       <c r="C2" t="n">
-        <v>3919</v>
+        <v>2691</v>
       </c>
       <c r="D2" t="n">
-        <v>13098</v>
+        <v>10644</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2336</v>
+        <v>2902</v>
       </c>
       <c r="C3" t="n">
-        <v>4082</v>
+        <v>3208</v>
       </c>
       <c r="D3" t="n">
-        <v>18554</v>
+        <v>14524</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2410</v>
+        <v>3078</v>
       </c>
       <c r="C4" t="n">
-        <v>5634</v>
+        <v>4278</v>
       </c>
       <c r="D4" t="n">
-        <v>14477</v>
+        <v>12738</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2057</v>
+        <v>2589</v>
       </c>
       <c r="C5" t="n">
-        <v>7671</v>
+        <v>5802</v>
       </c>
       <c r="D5" t="n">
-        <v>6950</v>
+        <v>6561</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1109</v>
+        <v>1376</v>
       </c>
       <c r="C6" t="n">
-        <v>6995</v>
+        <v>5742</v>
       </c>
       <c r="D6" t="n">
-        <v>2361</v>
+        <v>2183</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>240</v>
+        <v>322</v>
       </c>
       <c r="C7" t="n">
-        <v>4575</v>
+        <v>4115</v>
       </c>
       <c r="D7" t="n">
-        <v>791</v>
+        <v>760</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C8" t="n">
-        <v>2228</v>
+        <v>2222</v>
       </c>
       <c r="D8" t="n">
-        <v>413</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>651</v>
+        <v>748</v>
       </c>
       <c r="D9" t="n">
-        <v>287</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="11">
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="D11" t="n">
         <v>136</v>
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
         <v>19</v>
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3903</v>
+        <v>3782</v>
       </c>
       <c r="C2" t="n">
-        <v>10725</v>
+        <v>9526</v>
       </c>
       <c r="D2" t="n">
-        <v>16539</v>
+        <v>20874</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1894</v>
+        <v>2383</v>
       </c>
       <c r="C3" t="n">
-        <v>3613</v>
+        <v>2653</v>
       </c>
       <c r="D3" t="n">
-        <v>16711</v>
+        <v>13214</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2072</v>
+        <v>2619</v>
       </c>
       <c r="C4" t="n">
-        <v>4876</v>
+        <v>3716</v>
       </c>
       <c r="D4" t="n">
-        <v>14623</v>
+        <v>12485</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2008</v>
+        <v>2544</v>
       </c>
       <c r="C5" t="n">
-        <v>6709</v>
+        <v>5037</v>
       </c>
       <c r="D5" t="n">
-        <v>7750</v>
+        <v>7251</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1318</v>
+        <v>1655</v>
       </c>
       <c r="C6" t="n">
-        <v>7190</v>
+        <v>5715</v>
       </c>
       <c r="D6" t="n">
-        <v>2903</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>445</v>
+        <v>601</v>
       </c>
       <c r="C7" t="n">
-        <v>5450</v>
+        <v>4791</v>
       </c>
       <c r="D7" t="n">
-        <v>967</v>
+        <v>933</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>90</v>
+        <v>117</v>
       </c>
       <c r="C8" t="n">
-        <v>3053</v>
+        <v>2907</v>
       </c>
       <c r="D8" t="n">
-        <v>449</v>
+        <v>461</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>1145</v>
+        <v>1260</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>353</v>
+        <v>398</v>
       </c>
       <c r="D10" t="n">
-        <v>184</v>
+        <v>192</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D12" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>39</v>
+      </c>
+      <c r="D14" t="n">
         <v>38</v>
-      </c>
-      <c r="D14" t="n">
-        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
         <v>7</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4540</v>
+        <v>4643</v>
       </c>
       <c r="C2" t="n">
-        <v>9307</v>
+        <v>8211</v>
       </c>
       <c r="D2" t="n">
-        <v>11587</v>
+        <v>4615</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2818</v>
+        <v>2678</v>
       </c>
       <c r="C2" t="n">
-        <v>6263</v>
+        <v>5334</v>
       </c>
       <c r="D2" t="n">
-        <v>12305</v>
+        <v>15364</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2596</v>
+        <v>3196</v>
       </c>
       <c r="C3" t="n">
-        <v>5438</v>
+        <v>4527</v>
       </c>
       <c r="D3" t="n">
-        <v>17951</v>
+        <v>14740</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2912</v>
+        <v>3684</v>
       </c>
       <c r="C4" t="n">
-        <v>7153</v>
+        <v>5371</v>
       </c>
       <c r="D4" t="n">
-        <v>14915</v>
+        <v>12937</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1254</v>
+        <v>1623</v>
       </c>
       <c r="C5" t="n">
-        <v>10022</v>
+        <v>7761</v>
       </c>
       <c r="D5" t="n">
-        <v>7002</v>
+        <v>6634</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>411</v>
+        <v>555</v>
       </c>
       <c r="C6" t="n">
-        <v>6679</v>
+        <v>5871</v>
       </c>
       <c r="D6" t="n">
-        <v>2246</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83</v>
+        <v>108</v>
       </c>
       <c r="C7" t="n">
-        <v>2991</v>
+        <v>2848</v>
       </c>
       <c r="D7" t="n">
-        <v>563</v>
+        <v>579</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C8" t="n">
-        <v>1122</v>
+        <v>1234</v>
       </c>
       <c r="D8" t="n">
-        <v>290</v>
+        <v>298</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>345</v>
+        <v>390</v>
       </c>
       <c r="D9" t="n">
-        <v>180</v>
+        <v>188</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="D10" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="D11" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>38</v>
+      </c>
+      <c r="D13" t="n">
         <v>37</v>
-      </c>
-      <c r="D13" t="n">
-        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
         <v>6</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6319</v>
+        <v>6544</v>
       </c>
       <c r="C2" t="n">
-        <v>5844</v>
+        <v>8019</v>
       </c>
       <c r="D2" t="n">
-        <v>31204</v>
+        <v>22733</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1930</v>
+        <v>1974</v>
       </c>
       <c r="C3" t="n">
-        <v>4690</v>
+        <v>4204</v>
       </c>
       <c r="D3" t="n">
-        <v>2585</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C6" t="n">
         <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>808</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8">
@@ -4655,7 +4655,7 @@
         <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D12" t="n">
         <v>199</v>
@@ -4669,7 +4669,7 @@
         <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D13" t="n">
         <v>170</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4754</v>
+        <v>6110</v>
       </c>
       <c r="C2" t="n">
-        <v>4712</v>
+        <v>4411</v>
       </c>
       <c r="D2" t="n">
-        <v>24364</v>
+        <v>24192</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3383</v>
+        <v>3494</v>
       </c>
       <c r="C3" t="n">
-        <v>4607</v>
+        <v>5487</v>
       </c>
       <c r="D3" t="n">
-        <v>7202</v>
+        <v>4891</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>872</v>
+        <v>892</v>
       </c>
       <c r="C4" t="n">
-        <v>2792</v>
+        <v>2506</v>
       </c>
       <c r="D4" t="n">
-        <v>1702</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="5">
@@ -4865,10 +4865,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C5" t="n">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="D5" t="n">
         <v>1198</v>
@@ -4882,10 +4882,10 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>853</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C8" t="n">
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -4921,7 +4921,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C9" t="n">
         <v>232</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" t="n">
         <v>192</v>
@@ -4952,7 +4952,7 @@
         <v>43</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
         <v>270</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4994,7 +4994,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D14" t="n">
         <v>146</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5025,7 +5025,7 @@
         <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4831</v>
+        <v>5707</v>
       </c>
       <c r="C2" t="n">
-        <v>7110</v>
+        <v>4432</v>
       </c>
       <c r="D2" t="n">
-        <v>38762</v>
+        <v>21487</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3333</v>
+        <v>3913</v>
       </c>
       <c r="C3" t="n">
-        <v>4043</v>
+        <v>4241</v>
       </c>
       <c r="D3" t="n">
-        <v>9429</v>
+        <v>7627</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1806</v>
+        <v>1861</v>
       </c>
       <c r="C4" t="n">
-        <v>3717</v>
+        <v>4142</v>
       </c>
       <c r="D4" t="n">
-        <v>2706</v>
+        <v>2079</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="C5" t="n">
-        <v>1624</v>
+        <v>1465</v>
       </c>
       <c r="D5" t="n">
-        <v>1242</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>903</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>629</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="9">
@@ -5238,7 +5238,7 @@
         <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10">
@@ -5246,7 +5246,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C10" t="n">
         <v>210</v>
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5277,7 +5277,7 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D12" t="n">
         <v>213</v>
@@ -5291,7 +5291,7 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5316,7 +5316,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>77</v>
@@ -5333,10 +5333,10 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5347,10 +5347,10 @@
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4688</v>
+        <v>5083</v>
       </c>
       <c r="C2" t="n">
-        <v>9092</v>
+        <v>5224</v>
       </c>
       <c r="D2" t="n">
-        <v>29105</v>
+        <v>18047</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3311</v>
+        <v>3946</v>
       </c>
       <c r="C3" t="n">
-        <v>4874</v>
+        <v>3776</v>
       </c>
       <c r="D3" t="n">
-        <v>13223</v>
+        <v>9196</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2152</v>
+        <v>2405</v>
       </c>
       <c r="C4" t="n">
-        <v>3776</v>
+        <v>4109</v>
       </c>
       <c r="D4" t="n">
-        <v>3850</v>
+        <v>3027</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>908</v>
+        <v>930</v>
       </c>
       <c r="C5" t="n">
-        <v>2675</v>
+        <v>2808</v>
       </c>
       <c r="D5" t="n">
-        <v>1445</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="C6" t="n">
-        <v>960</v>
+        <v>891</v>
       </c>
       <c r="D6" t="n">
-        <v>953</v>
+        <v>941</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C7" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D7" t="n">
-        <v>666</v>
+        <v>662</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C8" t="n">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="D8" t="n">
-        <v>471</v>
+        <v>480</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="D9" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="10">
@@ -5557,10 +5557,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D10" t="n">
         <v>342</v>
@@ -5574,7 +5574,7 @@
         <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="D11" t="n">
         <v>286</v>
@@ -5585,7 +5585,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" t="n">
         <v>158</v>
@@ -5602,7 +5602,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D13" t="n">
         <v>176</v>
@@ -5619,7 +5619,7 @@
         <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5661,7 +5661,7 @@
         <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>60</v>
@@ -5686,7 +5686,7 @@
         <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6122</v>
+        <v>6052</v>
       </c>
       <c r="C2" t="n">
-        <v>8710</v>
+        <v>3864</v>
       </c>
       <c r="D2" t="n">
-        <v>24452</v>
+        <v>36923</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2919</v>
+        <v>3278</v>
       </c>
       <c r="C3" t="n">
-        <v>5728</v>
+        <v>3699</v>
       </c>
       <c r="D3" t="n">
-        <v>13836</v>
+        <v>9309</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1673</v>
+        <v>1956</v>
       </c>
       <c r="C4" t="n">
-        <v>3547</v>
+        <v>3215</v>
       </c>
       <c r="D4" t="n">
-        <v>4751</v>
+        <v>3543</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>787</v>
+        <v>866</v>
       </c>
       <c r="C5" t="n">
-        <v>2367</v>
+        <v>2521</v>
       </c>
       <c r="D5" t="n">
-        <v>1460</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="C6" t="n">
-        <v>1217</v>
+        <v>1251</v>
       </c>
       <c r="D6" t="n">
-        <v>789</v>
+        <v>763</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>391</v>
       </c>
       <c r="D7" t="n">
-        <v>518</v>
+        <v>514</v>
       </c>
     </row>
     <row r="8">
@@ -5846,7 +5846,7 @@
         <v>223</v>
       </c>
       <c r="D8" t="n">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="D9" t="n">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
         <v>150</v>
       </c>
       <c r="D10" t="n">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13">
@@ -5910,10 +5910,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D13" t="n">
         <v>117</v>
@@ -5941,10 +5941,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -5980,7 +5980,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
         <v>33</v>
@@ -6011,7 +6011,7 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>15</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5402</v>
+        <v>5550</v>
       </c>
       <c r="C2" t="n">
-        <v>4837</v>
+        <v>5926</v>
       </c>
       <c r="D2" t="n">
-        <v>20328</v>
+        <v>28366</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3740</v>
+        <v>3878</v>
       </c>
       <c r="C3" t="n">
-        <v>6409</v>
+        <v>3261</v>
       </c>
       <c r="D3" t="n">
-        <v>14601</v>
+        <v>13263</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2005</v>
+        <v>2296</v>
       </c>
       <c r="C4" t="n">
-        <v>4737</v>
+        <v>3440</v>
       </c>
       <c r="D4" t="n">
-        <v>6438</v>
+        <v>4563</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1083</v>
+        <v>1258</v>
       </c>
       <c r="C5" t="n">
-        <v>3008</v>
+        <v>2850</v>
       </c>
       <c r="D5" t="n">
-        <v>2033</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>489</v>
+        <v>524</v>
       </c>
       <c r="C6" t="n">
-        <v>1853</v>
+        <v>1967</v>
       </c>
       <c r="D6" t="n">
-        <v>906</v>
+        <v>846</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="C7" t="n">
-        <v>860</v>
+        <v>879</v>
       </c>
       <c r="D7" t="n">
-        <v>558</v>
+        <v>550</v>
       </c>
     </row>
     <row r="8">
@@ -6154,10 +6154,10 @@
         <v>66</v>
       </c>
       <c r="C8" t="n">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="D8" t="n">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12">
@@ -6213,7 +6213,7 @@
         <v>102</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14">
@@ -6297,7 +6297,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6322,7 +6322,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3890</v>
+        <v>6609</v>
       </c>
       <c r="C2" t="n">
-        <v>4300</v>
+        <v>8271</v>
       </c>
       <c r="D2" t="n">
-        <v>23589</v>
+        <v>20512</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3731</v>
+        <v>3860</v>
       </c>
       <c r="C3" t="n">
-        <v>4828</v>
+        <v>4080</v>
       </c>
       <c r="D3" t="n">
-        <v>14466</v>
+        <v>14724</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2434</v>
+        <v>2636</v>
       </c>
       <c r="C4" t="n">
-        <v>5569</v>
+        <v>3267</v>
       </c>
       <c r="D4" t="n">
-        <v>7809</v>
+        <v>6094</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1353</v>
+        <v>1566</v>
       </c>
       <c r="C5" t="n">
-        <v>3846</v>
+        <v>3086</v>
       </c>
       <c r="D5" t="n">
-        <v>2774</v>
+        <v>2135</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>703</v>
+        <v>800</v>
       </c>
       <c r="C6" t="n">
-        <v>2441</v>
+        <v>2418</v>
       </c>
       <c r="D6" t="n">
-        <v>1079</v>
+        <v>985</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>284</v>
+        <v>304</v>
       </c>
       <c r="C7" t="n">
-        <v>1375</v>
+        <v>1454</v>
       </c>
       <c r="D7" t="n">
-        <v>613</v>
+        <v>591</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C8" t="n">
-        <v>591</v>
+        <v>602</v>
       </c>
       <c r="D8" t="n">
-        <v>404</v>
+        <v>410</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10">
@@ -6490,10 +6490,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D10" t="n">
         <v>239</v>
@@ -6507,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -6566,7 +6566,7 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6608,7 +6608,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6630,10 +6630,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6647,7 +6647,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D21" t="n">
         <v>7</v>

--- a/output/yearly_population_iteration_61_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_61_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6387</v>
+        <v>850</v>
       </c>
       <c r="C2" t="n">
-        <v>6275</v>
+        <v>2412</v>
       </c>
       <c r="D2" t="n">
-        <v>33789</v>
+        <v>9807</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4208</v>
+        <v>1605</v>
       </c>
       <c r="C3" t="n">
-        <v>5401</v>
+        <v>4578</v>
       </c>
       <c r="D3" t="n">
-        <v>14567</v>
+        <v>12016</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2770</v>
+        <v>1077</v>
       </c>
       <c r="C4" t="n">
-        <v>3628</v>
+        <v>6951</v>
       </c>
       <c r="D4" t="n">
-        <v>7482</v>
+        <v>6109</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1812</v>
+        <v>478</v>
       </c>
       <c r="C5" t="n">
-        <v>3084</v>
+        <v>4687</v>
       </c>
       <c r="D5" t="n">
-        <v>2733</v>
+        <v>2038</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1050</v>
+        <v>204</v>
       </c>
       <c r="C6" t="n">
-        <v>2725</v>
+        <v>1528</v>
       </c>
       <c r="D6" t="n">
-        <v>1170</v>
+        <v>763</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>479</v>
+        <v>97</v>
       </c>
       <c r="C7" t="n">
-        <v>1925</v>
+        <v>491</v>
       </c>
       <c r="D7" t="n">
-        <v>650</v>
+        <v>497</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>168</v>
+        <v>74</v>
       </c>
       <c r="C8" t="n">
-        <v>996</v>
+        <v>323</v>
       </c>
       <c r="D8" t="n">
-        <v>430</v>
+        <v>370</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>416</v>
+        <v>292</v>
       </c>
       <c r="D9" t="n">
-        <v>310</v>
+        <v>321</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D10" t="n">
-        <v>242</v>
+        <v>268</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>142</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7282</v>
+        <v>647</v>
       </c>
       <c r="C2" t="n">
-        <v>6718</v>
+        <v>6712</v>
       </c>
       <c r="D2" t="n">
-        <v>31318</v>
+        <v>16131</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4225</v>
+        <v>1044</v>
       </c>
       <c r="C3" t="n">
-        <v>5100</v>
+        <v>2940</v>
       </c>
       <c r="D3" t="n">
-        <v>16202</v>
+        <v>10797</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2898</v>
+        <v>1161</v>
       </c>
       <c r="C4" t="n">
-        <v>4420</v>
+        <v>5529</v>
       </c>
       <c r="D4" t="n">
-        <v>8338</v>
+        <v>7057</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1988</v>
+        <v>669</v>
       </c>
       <c r="C5" t="n">
-        <v>3246</v>
+        <v>5851</v>
       </c>
       <c r="D5" t="n">
-        <v>3424</v>
+        <v>2718</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1254</v>
+        <v>302</v>
       </c>
       <c r="C6" t="n">
-        <v>2863</v>
+        <v>3118</v>
       </c>
       <c r="D6" t="n">
-        <v>1382</v>
+        <v>972</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>647</v>
+        <v>130</v>
       </c>
       <c r="C7" t="n">
-        <v>2284</v>
+        <v>1018</v>
       </c>
       <c r="D7" t="n">
-        <v>724</v>
+        <v>541</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>264</v>
+        <v>79</v>
       </c>
       <c r="C8" t="n">
-        <v>1386</v>
+        <v>403</v>
       </c>
       <c r="D8" t="n">
-        <v>453</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>93</v>
+        <v>57</v>
       </c>
       <c r="C9" t="n">
-        <v>660</v>
+        <v>310</v>
       </c>
       <c r="D9" t="n">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>295</v>
+        <v>249</v>
       </c>
       <c r="D10" t="n">
-        <v>248</v>
+        <v>271</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>217</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>178</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>94</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8503</v>
+        <v>335</v>
       </c>
       <c r="C2" t="n">
-        <v>7541</v>
+        <v>2671</v>
       </c>
       <c r="D2" t="n">
-        <v>33206</v>
+        <v>10884</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4467</v>
+        <v>889</v>
       </c>
       <c r="C3" t="n">
-        <v>5116</v>
+        <v>4347</v>
       </c>
       <c r="D3" t="n">
-        <v>17073</v>
+        <v>11186</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2959</v>
+        <v>1262</v>
       </c>
       <c r="C4" t="n">
-        <v>4585</v>
+        <v>4929</v>
       </c>
       <c r="D4" t="n">
-        <v>9292</v>
+        <v>7612</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2089</v>
+        <v>671</v>
       </c>
       <c r="C5" t="n">
-        <v>3654</v>
+        <v>6479</v>
       </c>
       <c r="D5" t="n">
-        <v>3994</v>
+        <v>3091</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1414</v>
+        <v>258</v>
       </c>
       <c r="C6" t="n">
-        <v>2998</v>
+        <v>4035</v>
       </c>
       <c r="D6" t="n">
-        <v>1657</v>
+        <v>992</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>800</v>
+        <v>74</v>
       </c>
       <c r="C7" t="n">
-        <v>2499</v>
+        <v>993</v>
       </c>
       <c r="D7" t="n">
-        <v>799</v>
+        <v>567</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>366</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>1746</v>
+        <v>453</v>
       </c>
       <c r="D8" t="n">
-        <v>485</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>139</v>
+        <v>28</v>
       </c>
       <c r="C9" t="n">
-        <v>930</v>
+        <v>244</v>
       </c>
       <c r="D9" t="n">
-        <v>333</v>
+        <v>368</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>427</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
-        <v>255</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>226</v>
+        <v>133</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>174</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>155</v>
+        <v>86</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>119</v>
+        <v>69</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
-        <v>103</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>92</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7763</v>
+        <v>548</v>
       </c>
       <c r="C2" t="n">
-        <v>5067</v>
+        <v>5928</v>
       </c>
       <c r="D2" t="n">
-        <v>27220</v>
+        <v>11104</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5375</v>
+        <v>537</v>
       </c>
       <c r="C3" t="n">
-        <v>7681</v>
+        <v>3033</v>
       </c>
       <c r="D3" t="n">
-        <v>18499</v>
+        <v>10439</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1930</v>
+        <v>972</v>
       </c>
       <c r="C4" t="n">
-        <v>6104</v>
+        <v>4555</v>
       </c>
       <c r="D4" t="n">
-        <v>8877</v>
+        <v>8032</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1306</v>
+        <v>835</v>
       </c>
       <c r="C5" t="n">
-        <v>2938</v>
+        <v>5602</v>
       </c>
       <c r="D5" t="n">
-        <v>2735</v>
+        <v>3778</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>739</v>
+        <v>395</v>
       </c>
       <c r="C6" t="n">
-        <v>2449</v>
+        <v>5267</v>
       </c>
       <c r="D6" t="n">
-        <v>783</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>338</v>
+        <v>128</v>
       </c>
       <c r="C7" t="n">
-        <v>1711</v>
+        <v>2413</v>
       </c>
       <c r="D7" t="n">
-        <v>475</v>
+        <v>629</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>128</v>
+        <v>56</v>
       </c>
       <c r="C8" t="n">
-        <v>911</v>
+        <v>689</v>
       </c>
       <c r="D8" t="n">
-        <v>326</v>
+        <v>455</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="C9" t="n">
-        <v>418</v>
+        <v>333</v>
       </c>
       <c r="D9" t="n">
-        <v>249</v>
+        <v>375</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="D10" t="n">
-        <v>200</v>
+        <v>227</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D11" t="n">
-        <v>161</v>
+        <v>179</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>125</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>77</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>89</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>102</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4645</v>
+        <v>346</v>
       </c>
       <c r="C2" t="n">
-        <v>2402</v>
+        <v>3323</v>
       </c>
       <c r="D2" t="n">
-        <v>19607</v>
+        <v>8760</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5522</v>
+        <v>472</v>
       </c>
       <c r="C3" t="n">
-        <v>5868</v>
+        <v>3940</v>
       </c>
       <c r="D3" t="n">
-        <v>18619</v>
+        <v>10016</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2819</v>
+        <v>757</v>
       </c>
       <c r="C4" t="n">
-        <v>6894</v>
+        <v>3846</v>
       </c>
       <c r="D4" t="n">
-        <v>10255</v>
+        <v>8234</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1465</v>
+        <v>865</v>
       </c>
       <c r="C5" t="n">
-        <v>4355</v>
+        <v>5292</v>
       </c>
       <c r="D5" t="n">
-        <v>3470</v>
+        <v>4307</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>886</v>
+        <v>492</v>
       </c>
       <c r="C6" t="n">
-        <v>2771</v>
+        <v>5607</v>
       </c>
       <c r="D6" t="n">
-        <v>983</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>316</v>
+        <v>148</v>
       </c>
       <c r="C7" t="n">
-        <v>2046</v>
+        <v>3472</v>
       </c>
       <c r="D7" t="n">
-        <v>519</v>
+        <v>700</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>107</v>
+        <v>54</v>
       </c>
       <c r="C8" t="n">
-        <v>1187</v>
+        <v>1144</v>
       </c>
       <c r="D8" t="n">
-        <v>340</v>
+        <v>491</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>477</v>
+        <v>434</v>
       </c>
       <c r="D9" t="n">
-        <v>257</v>
+        <v>377</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C10" t="n">
         <v>235</v>
       </c>
       <c r="D10" t="n">
-        <v>209</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>188</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>87</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4732</v>
+        <v>1379</v>
       </c>
       <c r="C2" t="n">
-        <v>5838</v>
+        <v>6885</v>
       </c>
       <c r="D2" t="n">
-        <v>18642</v>
+        <v>8699</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4326</v>
+        <v>351</v>
       </c>
       <c r="C3" t="n">
-        <v>3722</v>
+        <v>3186</v>
       </c>
       <c r="D3" t="n">
-        <v>17480</v>
+        <v>9146</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3417</v>
+        <v>559</v>
       </c>
       <c r="C4" t="n">
-        <v>6238</v>
+        <v>3850</v>
       </c>
       <c r="D4" t="n">
-        <v>11388</v>
+        <v>8291</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1813</v>
+        <v>761</v>
       </c>
       <c r="C5" t="n">
-        <v>5483</v>
+        <v>4487</v>
       </c>
       <c r="D5" t="n">
-        <v>4471</v>
+        <v>4816</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1049</v>
+        <v>595</v>
       </c>
       <c r="C6" t="n">
-        <v>3500</v>
+        <v>5460</v>
       </c>
       <c r="D6" t="n">
-        <v>1351</v>
+        <v>1992</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>477</v>
+        <v>248</v>
       </c>
       <c r="C7" t="n">
-        <v>2384</v>
+        <v>4412</v>
       </c>
       <c r="D7" t="n">
-        <v>581</v>
+        <v>824</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>158</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>1551</v>
+        <v>2135</v>
       </c>
       <c r="D8" t="n">
-        <v>364</v>
+        <v>514</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="C9" t="n">
-        <v>752</v>
+        <v>716</v>
       </c>
       <c r="D9" t="n">
-        <v>264</v>
+        <v>391</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>324</v>
+        <v>311</v>
       </c>
       <c r="D10" t="n">
-        <v>214</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
+        <v>186</v>
+      </c>
+      <c r="D11" t="n">
         <v>192</v>
-      </c>
-      <c r="D11" t="n">
-        <v>170</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>134</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>103</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2782</v>
+        <v>904</v>
       </c>
       <c r="C2" t="n">
-        <v>2692</v>
+        <v>3470</v>
       </c>
       <c r="D2" t="n">
-        <v>12870</v>
+        <v>6264</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4268</v>
+        <v>645</v>
       </c>
       <c r="C3" t="n">
-        <v>4330</v>
+        <v>4515</v>
       </c>
       <c r="D3" t="n">
-        <v>17190</v>
+        <v>9706</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3782</v>
+        <v>968</v>
       </c>
       <c r="C4" t="n">
-        <v>5861</v>
+        <v>5354</v>
       </c>
       <c r="D4" t="n">
-        <v>12173</v>
+        <v>8745</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1890</v>
+        <v>613</v>
       </c>
       <c r="C5" t="n">
-        <v>6409</v>
+        <v>7136</v>
       </c>
       <c r="D5" t="n">
-        <v>4875</v>
+        <v>4543</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>876</v>
+        <v>229</v>
       </c>
       <c r="C6" t="n">
-        <v>4385</v>
+        <v>5768</v>
       </c>
       <c r="D6" t="n">
-        <v>1314</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>72</v>
       </c>
       <c r="C7" t="n">
-        <v>2645</v>
+        <v>2092</v>
       </c>
       <c r="D7" t="n">
-        <v>586</v>
+        <v>624</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="C8" t="n">
-        <v>1223</v>
+        <v>701</v>
       </c>
       <c r="D8" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>317</v>
+        <v>304</v>
       </c>
       <c r="D9" t="n">
-        <v>289</v>
+        <v>242</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
+        <v>182</v>
+      </c>
+      <c r="D10" t="n">
         <v>188</v>
-      </c>
-      <c r="D10" t="n">
-        <v>166</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="D11" t="n">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3718</v>
+        <v>447</v>
       </c>
       <c r="C2" t="n">
-        <v>4139</v>
+        <v>1920</v>
       </c>
       <c r="D2" t="n">
-        <v>14765</v>
+        <v>5383</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3116</v>
+        <v>634</v>
       </c>
       <c r="C3" t="n">
-        <v>3135</v>
+        <v>3496</v>
       </c>
       <c r="D3" t="n">
-        <v>15447</v>
+        <v>8473</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3484</v>
+        <v>681</v>
       </c>
       <c r="C4" t="n">
-        <v>5045</v>
+        <v>4664</v>
       </c>
       <c r="D4" t="n">
-        <v>12621</v>
+        <v>8306</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2362</v>
+        <v>555</v>
       </c>
       <c r="C5" t="n">
-        <v>6084</v>
+        <v>5510</v>
       </c>
       <c r="D5" t="n">
-        <v>5847</v>
+        <v>4671</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1159</v>
+        <v>226</v>
       </c>
       <c r="C6" t="n">
-        <v>5261</v>
+        <v>5319</v>
       </c>
       <c r="D6" t="n">
-        <v>1822</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>331</v>
+        <v>61</v>
       </c>
       <c r="C7" t="n">
-        <v>3411</v>
+        <v>2710</v>
       </c>
       <c r="D7" t="n">
-        <v>672</v>
+        <v>616</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>15</v>
       </c>
       <c r="C8" t="n">
-        <v>1776</v>
+        <v>831</v>
       </c>
       <c r="D8" t="n">
-        <v>404</v>
+        <v>332</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>628</v>
+        <v>282</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>193</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>231</v>
+        <v>137</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>101</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>83</v>
+        <v>55</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2715</v>
+        <v>604</v>
       </c>
       <c r="C2" t="n">
-        <v>2691</v>
+        <v>4657</v>
       </c>
       <c r="D2" t="n">
-        <v>10644</v>
+        <v>13105</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2902</v>
+        <v>454</v>
       </c>
       <c r="C3" t="n">
-        <v>3208</v>
+        <v>2279</v>
       </c>
       <c r="D3" t="n">
-        <v>14524</v>
+        <v>7411</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3078</v>
+        <v>572</v>
       </c>
       <c r="C4" t="n">
-        <v>4278</v>
+        <v>3894</v>
       </c>
       <c r="D4" t="n">
-        <v>12738</v>
+        <v>8085</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2589</v>
+        <v>559</v>
       </c>
       <c r="C5" t="n">
-        <v>5802</v>
+        <v>4977</v>
       </c>
       <c r="D5" t="n">
-        <v>6561</v>
+        <v>5192</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1376</v>
+        <v>348</v>
       </c>
       <c r="C6" t="n">
-        <v>5742</v>
+        <v>5359</v>
       </c>
       <c r="D6" t="n">
-        <v>2183</v>
+        <v>2268</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>322</v>
+        <v>120</v>
       </c>
       <c r="C7" t="n">
-        <v>4115</v>
+        <v>4090</v>
       </c>
       <c r="D7" t="n">
-        <v>760</v>
+        <v>806</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="C8" t="n">
-        <v>2222</v>
+        <v>1759</v>
       </c>
       <c r="D8" t="n">
-        <v>427</v>
+        <v>373</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>748</v>
+        <v>537</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>211</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>202</v>
       </c>
       <c r="D10" t="n">
-        <v>182</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>135</v>
+        <v>103</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>105</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3782</v>
+        <v>769</v>
       </c>
       <c r="C2" t="n">
-        <v>9526</v>
+        <v>18382</v>
       </c>
       <c r="D2" t="n">
-        <v>20874</v>
+        <v>11938</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2383</v>
+        <v>431</v>
       </c>
       <c r="C3" t="n">
-        <v>2653</v>
+        <v>3048</v>
       </c>
       <c r="D3" t="n">
-        <v>13214</v>
+        <v>7754</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2619</v>
+        <v>450</v>
       </c>
       <c r="C4" t="n">
-        <v>3716</v>
+        <v>2944</v>
       </c>
       <c r="D4" t="n">
-        <v>12485</v>
+        <v>7716</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2544</v>
+        <v>508</v>
       </c>
       <c r="C5" t="n">
-        <v>5037</v>
+        <v>4312</v>
       </c>
       <c r="D5" t="n">
-        <v>7251</v>
+        <v>5534</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1655</v>
+        <v>411</v>
       </c>
       <c r="C6" t="n">
-        <v>5715</v>
+        <v>5110</v>
       </c>
       <c r="D6" t="n">
-        <v>2743</v>
+        <v>2692</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>601</v>
+        <v>199</v>
       </c>
       <c r="C7" t="n">
-        <v>4791</v>
+        <v>4710</v>
       </c>
       <c r="D7" t="n">
-        <v>933</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>117</v>
+        <v>60</v>
       </c>
       <c r="C8" t="n">
-        <v>2907</v>
+        <v>2854</v>
       </c>
       <c r="D8" t="n">
-        <v>461</v>
+        <v>437</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>1260</v>
+        <v>1087</v>
       </c>
       <c r="D9" t="n">
-        <v>305</v>
+        <v>230</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>398</v>
+        <v>346</v>
       </c>
       <c r="D10" t="n">
-        <v>192</v>
+        <v>157</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>143</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4643</v>
+        <v>2018</v>
       </c>
       <c r="C2" t="n">
-        <v>8211</v>
+        <v>2312</v>
       </c>
       <c r="D2" t="n">
-        <v>4615</v>
+        <v>12401</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2678</v>
+        <v>489</v>
       </c>
       <c r="C2" t="n">
-        <v>5334</v>
+        <v>22383</v>
       </c>
       <c r="D2" t="n">
-        <v>15364</v>
+        <v>16919</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3196</v>
+        <v>471</v>
       </c>
       <c r="C3" t="n">
-        <v>4527</v>
+        <v>8933</v>
       </c>
       <c r="D3" t="n">
-        <v>14740</v>
+        <v>7801</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3684</v>
+        <v>380</v>
       </c>
       <c r="C4" t="n">
-        <v>5371</v>
+        <v>2933</v>
       </c>
       <c r="D4" t="n">
-        <v>12937</v>
+        <v>7413</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1623</v>
+        <v>443</v>
       </c>
       <c r="C5" t="n">
-        <v>7761</v>
+        <v>3578</v>
       </c>
       <c r="D5" t="n">
-        <v>6634</v>
+        <v>5721</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>555</v>
+        <v>418</v>
       </c>
       <c r="C6" t="n">
-        <v>5871</v>
+        <v>4649</v>
       </c>
       <c r="D6" t="n">
-        <v>2130</v>
+        <v>3092</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>108</v>
+        <v>261</v>
       </c>
       <c r="C7" t="n">
-        <v>2848</v>
+        <v>4888</v>
       </c>
       <c r="D7" t="n">
-        <v>579</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="C8" t="n">
-        <v>1234</v>
+        <v>3653</v>
       </c>
       <c r="D8" t="n">
-        <v>298</v>
+        <v>521</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>390</v>
+        <v>1813</v>
       </c>
       <c r="D9" t="n">
-        <v>188</v>
+        <v>253</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>162</v>
+        <v>632</v>
       </c>
       <c r="D10" t="n">
-        <v>135</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>93</v>
+        <v>220</v>
       </c>
       <c r="D11" t="n">
-        <v>92</v>
+        <v>114</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>51</v>
+        <v>102</v>
       </c>
       <c r="D12" t="n">
-        <v>61</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
         <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>67</v>
+        <v>34</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6544</v>
+        <v>3669</v>
       </c>
       <c r="C2" t="n">
-        <v>8019</v>
+        <v>10987</v>
       </c>
       <c r="D2" t="n">
-        <v>22733</v>
+        <v>22416</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1974</v>
+        <v>670</v>
       </c>
       <c r="C3" t="n">
-        <v>4204</v>
+        <v>913</v>
       </c>
       <c r="D3" t="n">
-        <v>1414</v>
+        <v>2306</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>334</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>360</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6110</v>
+        <v>2172</v>
       </c>
       <c r="C2" t="n">
-        <v>4411</v>
+        <v>8252</v>
       </c>
       <c r="D2" t="n">
-        <v>24192</v>
+        <v>19734</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3494</v>
+        <v>1847</v>
       </c>
       <c r="C3" t="n">
-        <v>5487</v>
+        <v>6020</v>
       </c>
       <c r="D3" t="n">
-        <v>4891</v>
+        <v>5671</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>892</v>
+        <v>337</v>
       </c>
       <c r="C4" t="n">
-        <v>2506</v>
+        <v>617</v>
       </c>
       <c r="D4" t="n">
-        <v>1466</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>124</v>
+        <v>98</v>
       </c>
       <c r="C5" t="n">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>137</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>340</v>
       </c>
       <c r="D6" t="n">
-        <v>853</v>
+        <v>756</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>114</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>324</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>245</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>190</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>160</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>139</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>134</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>186</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5707</v>
+        <v>2001</v>
       </c>
       <c r="C2" t="n">
-        <v>4432</v>
+        <v>6101</v>
       </c>
       <c r="D2" t="n">
-        <v>21487</v>
+        <v>19633</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3913</v>
+        <v>1658</v>
       </c>
       <c r="C3" t="n">
-        <v>4241</v>
+        <v>6297</v>
       </c>
       <c r="D3" t="n">
-        <v>7627</v>
+        <v>7616</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1861</v>
+        <v>958</v>
       </c>
       <c r="C4" t="n">
-        <v>4142</v>
+        <v>3871</v>
       </c>
       <c r="D4" t="n">
-        <v>2079</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>419</v>
+        <v>192</v>
       </c>
       <c r="C5" t="n">
-        <v>1465</v>
+        <v>442</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>111</v>
       </c>
       <c r="C6" t="n">
-        <v>304</v>
+        <v>259</v>
       </c>
       <c r="D6" t="n">
-        <v>903</v>
+        <v>799</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>117</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>332</v>
       </c>
       <c r="D7" t="n">
-        <v>629</v>
+        <v>549</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>287</v>
       </c>
       <c r="D8" t="n">
-        <v>456</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>218</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>174</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>193</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5083</v>
+        <v>1696</v>
       </c>
       <c r="C2" t="n">
-        <v>5224</v>
+        <v>3732</v>
       </c>
       <c r="D2" t="n">
-        <v>18047</v>
+        <v>23466</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3946</v>
+        <v>1506</v>
       </c>
       <c r="C3" t="n">
-        <v>3776</v>
+        <v>5346</v>
       </c>
       <c r="D3" t="n">
-        <v>9196</v>
+        <v>8990</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2405</v>
+        <v>1130</v>
       </c>
       <c r="C4" t="n">
-        <v>4109</v>
+        <v>5187</v>
       </c>
       <c r="D4" t="n">
-        <v>3027</v>
+        <v>3261</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>930</v>
+        <v>485</v>
       </c>
       <c r="C5" t="n">
-        <v>2808</v>
+        <v>2342</v>
       </c>
       <c r="D5" t="n">
-        <v>1302</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>249</v>
+        <v>139</v>
       </c>
       <c r="C6" t="n">
-        <v>891</v>
+        <v>354</v>
       </c>
       <c r="D6" t="n">
-        <v>941</v>
+        <v>845</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>107</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>293</v>
       </c>
       <c r="D7" t="n">
-        <v>662</v>
+        <v>582</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>376</v>
+        <v>309</v>
       </c>
       <c r="D8" t="n">
-        <v>480</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="C9" t="n">
-        <v>310</v>
+        <v>249</v>
       </c>
       <c r="D9" t="n">
-        <v>381</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>195</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>160</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>199</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6052</v>
+        <v>2224</v>
       </c>
       <c r="C2" t="n">
-        <v>3864</v>
+        <v>5887</v>
       </c>
       <c r="D2" t="n">
-        <v>36923</v>
+        <v>20788</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3278</v>
+        <v>1318</v>
       </c>
       <c r="C3" t="n">
-        <v>3699</v>
+        <v>3908</v>
       </c>
       <c r="D3" t="n">
-        <v>9309</v>
+        <v>10557</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1956</v>
+        <v>1135</v>
       </c>
       <c r="C4" t="n">
-        <v>3215</v>
+        <v>5166</v>
       </c>
       <c r="D4" t="n">
-        <v>3543</v>
+        <v>4175</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>866</v>
+        <v>693</v>
       </c>
       <c r="C5" t="n">
-        <v>2521</v>
+        <v>3795</v>
       </c>
       <c r="D5" t="n">
-        <v>1253</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="C6" t="n">
-        <v>1251</v>
+        <v>1358</v>
       </c>
       <c r="D6" t="n">
-        <v>763</v>
+        <v>915</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C7" t="n">
-        <v>391</v>
+        <v>323</v>
       </c>
       <c r="D7" t="n">
-        <v>514</v>
+        <v>614</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="C8" t="n">
-        <v>223</v>
+        <v>301</v>
       </c>
       <c r="D8" t="n">
-        <v>361</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>199</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>271</v>
+        <v>345</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>219</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>175</v>
       </c>
       <c r="D11" t="n">
-        <v>193</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>143</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>202</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>118</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,10 +6022,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5550</v>
+        <v>1901</v>
       </c>
       <c r="C2" t="n">
-        <v>5926</v>
+        <v>6044</v>
       </c>
       <c r="D2" t="n">
-        <v>28366</v>
+        <v>17710</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3878</v>
+        <v>1418</v>
       </c>
       <c r="C3" t="n">
-        <v>3261</v>
+        <v>4268</v>
       </c>
       <c r="D3" t="n">
-        <v>13263</v>
+        <v>11303</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2296</v>
+        <v>1056</v>
       </c>
       <c r="C4" t="n">
-        <v>3440</v>
+        <v>4406</v>
       </c>
       <c r="D4" t="n">
-        <v>4563</v>
+        <v>5110</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1258</v>
+        <v>787</v>
       </c>
       <c r="C5" t="n">
-        <v>2850</v>
+        <v>4364</v>
       </c>
       <c r="D5" t="n">
-        <v>1676</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>524</v>
+        <v>418</v>
       </c>
       <c r="C6" t="n">
-        <v>1967</v>
+        <v>2536</v>
       </c>
       <c r="D6" t="n">
-        <v>846</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C7" t="n">
-        <v>879</v>
+        <v>819</v>
       </c>
       <c r="D7" t="n">
-        <v>550</v>
+        <v>657</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>469</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>284</v>
       </c>
       <c r="D9" t="n">
-        <v>281</v>
+        <v>353</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>243</v>
       </c>
       <c r="D10" t="n">
-        <v>238</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>193</v>
       </c>
       <c r="D11" t="n">
-        <v>198</v>
+        <v>263</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>155</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>208</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>126</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>165</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21">
@@ -6333,10 +6333,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6609</v>
+        <v>1738</v>
       </c>
       <c r="C2" t="n">
-        <v>8271</v>
+        <v>3674</v>
       </c>
       <c r="D2" t="n">
-        <v>20512</v>
+        <v>13851</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3860</v>
+        <v>1890</v>
       </c>
       <c r="C3" t="n">
-        <v>4080</v>
+        <v>6653</v>
       </c>
       <c r="D3" t="n">
-        <v>14724</v>
+        <v>12590</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2636</v>
+        <v>727</v>
       </c>
       <c r="C4" t="n">
-        <v>3267</v>
+        <v>7023</v>
       </c>
       <c r="D4" t="n">
-        <v>6094</v>
+        <v>4821</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1566</v>
+        <v>386</v>
       </c>
       <c r="C5" t="n">
-        <v>3086</v>
+        <v>2485</v>
       </c>
       <c r="D5" t="n">
-        <v>2135</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>800</v>
+        <v>150</v>
       </c>
       <c r="C6" t="n">
-        <v>2418</v>
+        <v>802</v>
       </c>
       <c r="D6" t="n">
-        <v>985</v>
+        <v>643</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
+        <v>86</v>
+      </c>
+      <c r="C7" t="n">
         <v>304</v>
       </c>
-      <c r="C7" t="n">
-        <v>1454</v>
-      </c>
       <c r="D7" t="n">
-        <v>591</v>
+        <v>459</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
-        <v>602</v>
+        <v>278</v>
       </c>
       <c r="D8" t="n">
-        <v>410</v>
+        <v>345</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>259</v>
+        <v>238</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D10" t="n">
-        <v>239</v>
+        <v>257</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
         <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>145</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
